--- a/outputs/paper_tables.xlsx
+++ b/outputs/paper_tables.xlsx
@@ -4250,7 +4250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ56"/>
+  <dimension ref="A1:AQ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Mg24</t>
+          <t>Mg24 h</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Si29</t>
+          <t>Si29 h</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Sc45</t>
+          <t>Sc45 h</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Mn55</t>
+          <t>Mn55 h</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Fe57</t>
+          <t>Fe57 h</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -14824,19 +14824,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ca43 (IS): internal standard, fixed in GLITTER to a value entered for each analysis; not measured or corrected.</t>
+          <t>h: in the inclusions, partly host olivine ablated with the inclusion: the major-element oxide sums range from 67 to 416 wt% and correlate with these elements (r = 0.69 to 0.99); not interpreted.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCR-2G: run 70 excluded (normalised to the wrong Ca in GLITTER). KL2 test split: runs 6, 26, 46, 67, 83, not used for the correction. KL2 precision: train and test analyses together.</t>
+          <t>Ca43 (IS): internal standard, fixed in GLITTER to a value entered for each analysis; not measured or corrected.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
+        <is>
+          <t>BCR-2G: run 70 excluded (normalised to the wrong Ca in GLITTER). KL2 test split: runs 6, 26, 46, 67, 83, not used for the correction. KL2 precision: train and test analyses together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Reference values: GeoReM (Standards.xlsx) ± 95 % uncertainty; CI chondrite and primitive mantle: Sun and McDonough (1989).</t>
         </is>
